--- a/data/trans_dic/P6904-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P6904-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que su trabajo le afecta de manera que tiene dolores musculares</t>
+          <t>Población que su trabajo le afecta de manera que tiene dolores musculares (tasa de respuesta: 99,68%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>38,49; 61,39</t>
+          <t>39,11; 61,1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>47,54; 69,26</t>
+          <t>46,06; 68,18</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>36,83; 65,81</t>
+          <t>36,73; 63,46</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>64,75; 85,11</t>
+          <t>64,15; 85,16</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>47,18; 80,0</t>
+          <t>46,05; 80,04</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45,92; 77,69</t>
+          <t>45,53; 76,81</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>53,81; 85,04</t>
+          <t>52,49; 85,34</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>49,45; 71,31</t>
+          <t>49,28; 71,24</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>45,4; 64,79</t>
+          <t>44,87; 63,91</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>48,86; 67,58</t>
+          <t>50,07; 68,41</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>47,21; 70,68</t>
+          <t>46,68; 69,28</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>61,42; 75,82</t>
+          <t>61,28; 76,4</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>39,45; 56,07</t>
+          <t>39,27; 56,98</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>47,46; 69,63</t>
+          <t>47,52; 68,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>54,84; 75,39</t>
+          <t>54,67; 75,34</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>54,45; 74,25</t>
+          <t>53,97; 72,54</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>30,49; 57,32</t>
+          <t>30,26; 57,97</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>41,43; 68,16</t>
+          <t>40,54; 68,0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>53,56; 79,51</t>
+          <t>53,35; 78,89</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>53,88; 70,6</t>
+          <t>54,37; 69,79</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>39,27; 54,14</t>
+          <t>39,86; 54,29</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>49,49; 65,62</t>
+          <t>47,96; 64,73</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>56,83; 73,99</t>
+          <t>58,17; 74,03</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>56,48; 69,8</t>
+          <t>56,42; 69,44</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>46,88; 66,15</t>
+          <t>46,48; 65,56</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>44,56; 67,36</t>
+          <t>44,53; 67,75</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>49,11; 67,92</t>
+          <t>49,32; 67,86</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>24,19; 50,47</t>
+          <t>24,09; 50,93</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>48,78; 76,9</t>
+          <t>49,61; 76,75</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>26,13; 52,97</t>
+          <t>25,65; 52,32</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>58,72; 80,87</t>
+          <t>58,44; 80,75</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>46,77; 87,37</t>
+          <t>48,0; 88,4</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>50,0; 65,84</t>
+          <t>49,78; 66,26</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>40,58; 58,68</t>
+          <t>41,07; 58,38</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>55,8; 70,64</t>
+          <t>55,43; 70,61</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>41,06; 79,34</t>
+          <t>41,57; 79,27</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>46,27; 63,89</t>
+          <t>45,36; 63,74</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>34,74; 56,4</t>
+          <t>35,63; 57,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>47,36; 69,09</t>
+          <t>47,86; 68,76</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>49,52; 71,27</t>
+          <t>51,57; 71,08</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>35,9; 58,49</t>
+          <t>35,79; 57,61</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>40,07; 65,35</t>
+          <t>40,03; 66,57</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>47,1; 72,32</t>
+          <t>49,1; 72,47</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>59,65; 76,36</t>
+          <t>58,86; 75,59</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>45,74; 57,83</t>
+          <t>44,58; 58,44</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>40,21; 57,89</t>
+          <t>40,43; 58,13</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>51,42; 67,79</t>
+          <t>52,34; 67,86</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>58,05; 71,52</t>
+          <t>57,55; 70,82</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>47,36; 56,78</t>
+          <t>47,09; 56,66</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>49,21; 60,81</t>
+          <t>49,14; 60,34</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>54,1; 64,93</t>
+          <t>54,09; 65,21</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>55,63; 67,07</t>
+          <t>55,66; 66,98</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>45,5; 59,0</t>
+          <t>44,96; 58,31</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>44,37; 58,36</t>
+          <t>44,95; 58,72</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>60,83; 73,65</t>
+          <t>60,93; 73,49</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>59,44; 75,25</t>
+          <t>59,7; 75,66</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>48,19; 55,86</t>
+          <t>48,28; 55,92</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>49,01; 58,03</t>
+          <t>49,26; 58,71</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>58,35; 66,58</t>
+          <t>58,47; 66,71</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>59,07; 69,2</t>
+          <t>59,13; 68,85</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que su trabajo le afecta de manera que tiene dolores musculares</t>
+          <t>Población que su trabajo le afecta de manera que tiene dolores musculares (tasa de respuesta: 99,68%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>30533; 48703</t>
+          <t>31030; 48473</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>36403; 53038</t>
+          <t>35270; 52214</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>20135; 35981</t>
+          <t>20081; 34696</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>46112; 60608</t>
+          <t>45681; 60649</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>15211; 25793</t>
+          <t>14846; 25807</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16188; 27390</t>
+          <t>16053; 27079</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16096; 25438</t>
+          <t>15702; 25528</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>27039; 38995</t>
+          <t>26945; 38955</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>50651; 72288</t>
+          <t>50064; 71301</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>54644; 75575</t>
+          <t>55991; 76504</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>39932; 59788</t>
+          <t>39485; 58599</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>77323; 95461</t>
+          <t>77144; 96181</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>57587; 81850</t>
+          <t>57333; 83173</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>43136; 63288</t>
+          <t>43189; 62316</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>53190; 73118</t>
+          <t>53017; 73068</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>60979; 83150</t>
+          <t>60432; 81238</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>16098; 30261</t>
+          <t>15976; 30607</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>25412; 41805</t>
+          <t>24863; 41705</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>29753; 44169</t>
+          <t>29635; 43827</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>53201; 69708</t>
+          <t>53678; 68900</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>78059; 107626</t>
+          <t>79227; 107912</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>75329; 99886</t>
+          <t>73001; 98526</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>86690; 112864</t>
+          <t>88725; 112923</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>119010; 147071</t>
+          <t>118894; 146319</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>51543; 72724</t>
+          <t>51100; 72084</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>35453; 53593</t>
+          <t>35425; 53901</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>53984; 74665</t>
+          <t>54216; 74604</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13372; 27898</t>
+          <t>13316; 28152</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>22698; 35784</t>
+          <t>23083; 35714</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13844; 28065</t>
+          <t>13590; 27719</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>38018; 52363</t>
+          <t>37835; 52285</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>45324; 84671</t>
+          <t>46515; 85664</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>78238; 103017</t>
+          <t>77892; 103689</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>53780; 77777</t>
+          <t>54430; 77377</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>97478; 123395</t>
+          <t>96828; 123349</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>62491; 120748</t>
+          <t>63270; 120638</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>63408; 87559</t>
+          <t>62167; 87359</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>27249; 44236</t>
+          <t>27947; 44738</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>41871; 61083</t>
+          <t>42312; 60792</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>50029; 72003</t>
+          <t>52097; 71810</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>31790; 51791</t>
+          <t>31692; 51011</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>25681; 41889</t>
+          <t>25657; 42671</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>31126; 47791</t>
+          <t>32447; 47892</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>61970; 79335</t>
+          <t>61151; 78537</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>103188; 130465</t>
+          <t>100569; 131851</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>57307; 82512</t>
+          <t>57629; 82852</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>79448; 104736</t>
+          <t>80861; 104836</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>118964; 146561</t>
+          <t>117940; 145136</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>223693; 268198</t>
+          <t>222390; 267606</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>160143; 197915</t>
+          <t>159921; 196372</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>189336; 227259</t>
+          <t>189315; 228223</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>188867; 227692</t>
+          <t>188962; 227403</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>100160; 129872</t>
+          <t>98975; 128347</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>94801; 124703</t>
+          <t>96046; 125458</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>131567; 159313</t>
+          <t>131790; 158949</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>210530; 266559</t>
+          <t>211471; 267993</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>333659; 386773</t>
+          <t>334291; 387206</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>264194; 312849</t>
+          <t>265561; 316514</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>330461; 377016</t>
+          <t>331123; 377794</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>409751; 480048</t>
+          <t>410195; 477653</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P6904-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P6904-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>75,97%</t>
+          <t>76,54%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>60,97%</t>
+          <t>60,36%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>69,46%</t>
+          <t>69,36%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>39,11; 61,1</t>
+          <t>38,91; 62,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>46,06; 68,18</t>
+          <t>47,57; 68,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>36,73; 63,46</t>
+          <t>38,14; 64,2</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>64,15; 85,16</t>
+          <t>64,44; 84,98</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>46,05; 80,04</t>
+          <t>47,72; 80,48</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45,53; 76,81</t>
+          <t>42,69; 77,58</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>52,49; 85,34</t>
+          <t>54,39; 85,3</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>49,28; 71,24</t>
+          <t>49,34; 70,64</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>44,87; 63,91</t>
+          <t>44,45; 63,66</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>50,07; 68,41</t>
+          <t>48,63; 67,64</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>46,68; 69,28</t>
+          <t>47,1; 68,76</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>61,28; 76,4</t>
+          <t>60,87; 76,25</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>64,36%</t>
+          <t>65,08%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>62,39%</t>
+          <t>61,74%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>63,43%</t>
+          <t>63,59%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>39,27; 56,98</t>
+          <t>39,56; 56,65</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>47,52; 68,57</t>
+          <t>48,48; 68,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>54,67; 75,34</t>
+          <t>54,46; 75,79</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>53,97; 72,54</t>
+          <t>54,4; 72,96</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>30,26; 57,97</t>
+          <t>29,18; 57,43</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>40,54; 68,0</t>
+          <t>41,51; 68,33</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>53,35; 78,89</t>
+          <t>53,92; 79,29</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>54,37; 69,79</t>
+          <t>53,32; 70,4</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>39,86; 54,29</t>
+          <t>39,44; 53,48</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>47,96; 64,73</t>
+          <t>48,85; 65,35</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>58,17; 74,03</t>
+          <t>58,04; 74,07</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>56,42; 69,44</t>
+          <t>57,01; 69,78</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>36,96%</t>
+          <t>47,25%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>68,09%</t>
+          <t>52,13%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>56,78%</t>
+          <t>49,72%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>46,48; 65,56</t>
+          <t>44,77; 66,67</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>44,53; 67,75</t>
+          <t>43,88; 67,56</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>49,32; 67,86</t>
+          <t>48,73; 67,61</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>24,09; 50,93</t>
+          <t>33,83; 60,45</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>49,61; 76,75</t>
+          <t>46,95; 76,81</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>25,65; 52,32</t>
+          <t>26,32; 53,6</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>58,44; 80,75</t>
+          <t>58,37; 80,73</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>48,0; 88,4</t>
+          <t>40,98; 63,21</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>49,78; 66,26</t>
+          <t>49,58; 66,05</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>41,07; 58,38</t>
+          <t>40,32; 57,93</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>55,43; 70,61</t>
+          <t>56,18; 70,63</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>41,57; 79,27</t>
+          <t>41,18; 59,1</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>61,54%</t>
+          <t>62,0%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>67,7%</t>
+          <t>66,31%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>64,66%</t>
+          <t>64,15%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>45,36; 63,74</t>
+          <t>46,57; 63,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>35,63; 57,04</t>
+          <t>34,36; 57,15</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>47,86; 68,76</t>
+          <t>48,76; 69,29</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>51,57; 71,08</t>
+          <t>51,81; 72,89</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>35,79; 57,61</t>
+          <t>36,01; 57,58</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>40,03; 66,57</t>
+          <t>39,54; 66,01</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>49,1; 72,47</t>
+          <t>48,07; 73,56</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>58,86; 75,59</t>
+          <t>57,53; 73,52</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>44,58; 58,44</t>
+          <t>45,0; 58,17</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>40,43; 58,13</t>
+          <t>40,29; 56,79</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>52,34; 67,86</t>
+          <t>52,28; 68,51</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>57,55; 70,82</t>
+          <t>57,34; 70,14</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>61,49%</t>
+          <t>63,26%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>65,29%</t>
+          <t>60,95%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>63,43%</t>
+          <t>62,17%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>47,09; 56,66</t>
+          <t>47,51; 57,21</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>49,14; 60,34</t>
+          <t>48,93; 61,16</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>54,09; 65,21</t>
+          <t>54,02; 65,28</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>55,66; 66,98</t>
+          <t>57,69; 68,31</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>44,96; 58,31</t>
+          <t>44,66; 58,32</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>44,95; 58,72</t>
+          <t>44,7; 58,16</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>60,93; 73,49</t>
+          <t>60,78; 73,25</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>59,7; 75,66</t>
+          <t>56,39; 65,61</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>48,28; 55,92</t>
+          <t>48,48; 56,12</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>49,26; 58,71</t>
+          <t>49,01; 58,39</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>58,47; 66,71</t>
+          <t>58,22; 66,58</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>59,13; 68,85</t>
+          <t>58,06; 65,58</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>54103</t>
+          <t>57440</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>33340</t>
+          <t>36109</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>87444</t>
+          <t>93548</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>31030; 48473</t>
+          <t>30868; 49320</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>35270; 52214</t>
+          <t>36432; 52484</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>20081; 34696</t>
+          <t>20851; 35099</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>45681; 60649</t>
+          <t>48360; 63770</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>14846; 25807</t>
+          <t>15385; 25948</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16053; 27079</t>
+          <t>15050; 27351</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15702; 25528</t>
+          <t>16270; 25519</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>26945; 38955</t>
+          <t>29517; 42260</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>50064; 71301</t>
+          <t>49599; 71023</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>55991; 76504</t>
+          <t>54386; 75646</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>39485; 58599</t>
+          <t>39837; 58162</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>77144; 96181</t>
+          <t>82086; 102833</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>72070</t>
+          <t>86557</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>61594</t>
+          <t>66340</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>133663</t>
+          <t>152898</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>57333; 83173</t>
+          <t>57747; 82696</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>43189; 62316</t>
+          <t>44059; 62410</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>53017; 73068</t>
+          <t>52816; 73504</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>60432; 81238</t>
+          <t>72351; 97034</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>15976; 30607</t>
+          <t>15406; 30319</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>24863; 41705</t>
+          <t>25460; 41908</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>29635; 43827</t>
+          <t>29951; 44048</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>53678; 68900</t>
+          <t>57292; 75649</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>79227; 107912</t>
+          <t>78400; 106302</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>73001; 98526</t>
+          <t>74360; 99472</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>88725; 112923</t>
+          <t>88525; 112979</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>118894; 146319</t>
+          <t>137079; 167782</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20429</t>
+          <t>32534</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>65988</t>
+          <t>36864</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>86417</t>
+          <t>69398</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>51100; 72084</t>
+          <t>49224; 73299</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>35425; 53901</t>
+          <t>34912; 53752</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>54216; 74604</t>
+          <t>53568; 74330</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13316; 28152</t>
+          <t>23293; 41627</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>23083; 35714</t>
+          <t>21846; 35743</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13590; 27719</t>
+          <t>13943; 28398</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>37835; 52285</t>
+          <t>37793; 52273</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>46515; 85664</t>
+          <t>28981; 44697</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>77892; 103689</t>
+          <t>77579; 103355</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>54430; 77377</t>
+          <t>53437; 76781</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>96828; 123349</t>
+          <t>98141; 123375</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>63270; 120638</t>
+          <t>57476; 82487</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>62172</t>
+          <t>67025</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>70337</t>
+          <t>71178</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>132509</t>
+          <t>138203</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>62167; 87359</t>
+          <t>63829; 87654</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>27947; 44738</t>
+          <t>26950; 44826</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>42312; 60792</t>
+          <t>43105; 61258</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>52097; 71810</t>
+          <t>56014; 78803</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>31692; 51011</t>
+          <t>31887; 50985</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>25657; 42671</t>
+          <t>25342; 42308</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>32447; 47892</t>
+          <t>31764; 48611</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>61151; 78537</t>
+          <t>61757; 78916</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>100569; 131851</t>
+          <t>101528; 131224</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>57629; 82852</t>
+          <t>57425; 80938</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>80861; 104836</t>
+          <t>80765; 105846</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>117940; 145136</t>
+          <t>123549; 151107</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>208774</t>
+          <t>243557</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>231260</t>
+          <t>210491</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>440034</t>
+          <t>454048</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>222390; 267606</t>
+          <t>224382; 270196</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>159921; 196372</t>
+          <t>159251; 199040</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>189315; 228223</t>
+          <t>189080; 228492</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>188962; 227403</t>
+          <t>222094; 262984</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>98975; 128347</t>
+          <t>98303; 128383</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>96046; 125458</t>
+          <t>95508; 124256</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>131790; 158949</t>
+          <t>131465; 158442</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>211471; 267993</t>
+          <t>194730; 226579</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>334291; 387206</t>
+          <t>335689; 388595</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>265561; 316514</t>
+          <t>264213; 314778</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>331123; 377794</t>
+          <t>329707; 377060</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>410195; 477653</t>
+          <t>424005; 478967</t>
         </is>
       </c>
     </row>
